--- a/test/s2t/s2t_27_csv_csv_bigdata_match.xlsx
+++ b/test/s2t/s2t_27_csv_csv_bigdata_match.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspaces\GitHub\QE_ATF\test\s2t\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My_Workspaces\GitHub\QE_ATF\test\s2t\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0F6CE6-A361-4457-A3E1-8A5EBF32A56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DA290C-7065-4386-BA01-FA1B96ABDEC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{60D25328-0517-4E51-B966-9D3337769260}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="10800" xr2:uid="{60D25328-0517-4E51-B966-9D3337769260}"/>
   </bookViews>
   <sheets>
     <sheet name="MappingConfiguration" sheetId="1" r:id="rId1"/>
@@ -320,12 +320,6 @@
     <t>ar_properties.csv</t>
   </si>
   <si>
-    <t>/app/test/data/source</t>
-  </si>
-  <si>
-    <t>/app/test/data/target</t>
-  </si>
-  <si>
     <t>ArgentinaPropertiesTgt</t>
   </si>
   <si>
@@ -420,6 +414,12 @@
   </si>
   <si>
     <t>stagedata</t>
+  </si>
+  <si>
+    <t>test/data/source</t>
+  </si>
+  <si>
+    <t>test/data/target</t>
   </si>
 </sst>
 </file>
@@ -899,7 +899,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -937,7 +937,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -979,7 +979,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1023,7 +1023,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1065,7 +1065,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1115,7 +1115,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1320,7 +1320,7 @@
         <v>65</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D3" s="6">
         <v>2</v>
@@ -1340,13 +1340,13 @@
         <v>65</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" s="6">
         <v>3</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>67</v>
@@ -1360,13 +1360,13 @@
         <v>65</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" s="6">
         <v>4</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>67</v>
@@ -1380,13 +1380,13 @@
         <v>65</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" s="6">
         <v>5</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>67</v>
@@ -1400,13 +1400,13 @@
         <v>65</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" s="6">
         <v>6</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>67</v>
@@ -1420,13 +1420,13 @@
         <v>65</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" s="6">
         <v>7</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>67</v>
@@ -1440,7 +1440,7 @@
         <v>65</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" s="6">
         <v>8</v>
@@ -1460,7 +1460,7 @@
         <v>65</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D10" s="6">
         <v>9</v>
@@ -1480,7 +1480,7 @@
         <v>65</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D11" s="6">
         <v>10</v>
@@ -1500,7 +1500,7 @@
         <v>65</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12" s="6">
         <v>11</v>
@@ -1520,7 +1520,7 @@
         <v>65</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" s="6">
         <v>12</v>
@@ -1540,7 +1540,7 @@
         <v>65</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D14" s="6">
         <v>13</v>
@@ -1560,13 +1560,13 @@
         <v>65</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D15" s="6">
         <v>14</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>67</v>
@@ -1580,13 +1580,13 @@
         <v>65</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D16" s="6">
         <v>15</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>67</v>
@@ -1600,13 +1600,13 @@
         <v>65</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D17" s="6">
         <v>16</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>67</v>
@@ -1620,13 +1620,13 @@
         <v>65</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18" s="6">
         <v>17</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>67</v>
@@ -1640,13 +1640,13 @@
         <v>65</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D19" s="6">
         <v>18</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>67</v>
@@ -1660,13 +1660,13 @@
         <v>65</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" s="6">
         <v>19</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>67</v>
@@ -1680,7 +1680,7 @@
         <v>65</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D21" s="6">
         <v>20</v>
@@ -1700,7 +1700,7 @@
         <v>65</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D22" s="6">
         <v>21</v>
@@ -1720,7 +1720,7 @@
         <v>65</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D23" s="6">
         <v>22</v>
@@ -1740,7 +1740,7 @@
         <v>65</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D24" s="6">
         <v>23</v>
@@ -1760,7 +1760,7 @@
         <v>65</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D25" s="6">
         <v>24</v>
@@ -1780,7 +1780,7 @@
         <v>65</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D26" s="6">
         <v>25</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>68</v>
@@ -1811,13 +1811,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D28" s="6">
         <v>2</v>
@@ -1831,19 +1831,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D29" s="6">
         <v>3</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F29" s="6" t="s">
         <v>67</v>
@@ -1851,19 +1851,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D30" s="6">
         <v>4</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>67</v>
@@ -1871,19 +1871,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D31" s="6">
         <v>5</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>67</v>
@@ -1891,19 +1891,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D32" s="6">
         <v>6</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>67</v>
@@ -1911,19 +1911,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D33" s="6">
         <v>7</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>67</v>
@@ -1931,13 +1931,13 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D34" s="6">
         <v>8</v>
@@ -1951,13 +1951,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D35" s="6">
         <v>9</v>
@@ -1971,13 +1971,13 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D36" s="6">
         <v>10</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D37" s="6">
         <v>11</v>
@@ -2011,13 +2011,13 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D38" s="6">
         <v>12</v>
@@ -2031,13 +2031,13 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D39" s="6">
         <v>13</v>
@@ -2051,19 +2051,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D40" s="6">
         <v>14</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>67</v>
@@ -2071,19 +2071,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D41" s="6">
         <v>15</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>67</v>
@@ -2091,19 +2091,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D42" s="6">
         <v>16</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>67</v>
@@ -2111,19 +2111,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D43" s="6">
         <v>17</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>67</v>
@@ -2131,19 +2131,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D44" s="6">
         <v>18</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>67</v>
@@ -2151,19 +2151,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D45" s="6">
         <v>19</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F45" s="6" t="s">
         <v>67</v>
@@ -2171,13 +2171,13 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D46" s="6">
         <v>20</v>
@@ -2191,13 +2191,13 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D47" s="6">
         <v>21</v>
@@ -2211,13 +2211,13 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D48" s="6">
         <v>22</v>
@@ -2231,13 +2231,13 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D49" s="6">
         <v>23</v>
@@ -2251,13 +2251,13 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D50" s="6">
         <v>24</v>
@@ -2271,13 +2271,13 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D51" s="6">
         <v>25</v>
@@ -2314,7 +2314,7 @@
         <v>87</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D53" s="6">
         <v>2</v>
@@ -2334,13 +2334,13 @@
         <v>87</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D54" s="6">
         <v>3</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>67</v>
@@ -2354,13 +2354,13 @@
         <v>87</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D55" s="6">
         <v>4</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>67</v>
@@ -2374,13 +2374,13 @@
         <v>87</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D56" s="6">
         <v>5</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>67</v>
@@ -2394,13 +2394,13 @@
         <v>87</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D57" s="6">
         <v>6</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F57" s="6" t="s">
         <v>67</v>
@@ -2414,13 +2414,13 @@
         <v>87</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D58" s="6">
         <v>7</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>67</v>
@@ -2434,7 +2434,7 @@
         <v>87</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D59" s="6">
         <v>8</v>
@@ -2454,7 +2454,7 @@
         <v>87</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D60" s="6">
         <v>9</v>
@@ -2474,7 +2474,7 @@
         <v>87</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D61" s="6">
         <v>10</v>
@@ -2494,7 +2494,7 @@
         <v>87</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D62" s="6">
         <v>11</v>
@@ -2514,7 +2514,7 @@
         <v>87</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D63" s="6">
         <v>12</v>
@@ -2534,7 +2534,7 @@
         <v>87</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D64" s="6">
         <v>13</v>
@@ -2554,13 +2554,13 @@
         <v>87</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D65" s="6">
         <v>14</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F65" s="6" t="s">
         <v>67</v>
@@ -2574,13 +2574,13 @@
         <v>87</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D66" s="6">
         <v>15</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>67</v>
@@ -2594,13 +2594,13 @@
         <v>87</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D67" s="6">
         <v>16</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>67</v>
@@ -2614,13 +2614,13 @@
         <v>87</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D68" s="6">
         <v>17</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>67</v>
@@ -2634,13 +2634,13 @@
         <v>87</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D69" s="6">
         <v>18</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>67</v>
@@ -2654,13 +2654,13 @@
         <v>87</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D70" s="6">
         <v>19</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>67</v>
@@ -2674,7 +2674,7 @@
         <v>87</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D71" s="6">
         <v>20</v>
@@ -2694,7 +2694,7 @@
         <v>87</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D72" s="6">
         <v>21</v>
@@ -2714,7 +2714,7 @@
         <v>87</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D73" s="6">
         <v>22</v>
@@ -2734,7 +2734,7 @@
         <v>87</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D74" s="6">
         <v>23</v>
@@ -2754,7 +2754,7 @@
         <v>87</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D75" s="6">
         <v>24</v>
@@ -2774,7 +2774,7 @@
         <v>87</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D76" s="6">
         <v>25</v>
@@ -2871,10 +2871,10 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>68</v>
@@ -2903,13 +2903,13 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>64</v>
@@ -2918,7 +2918,7 @@
         <v>65</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>82</v>
@@ -2935,13 +2935,13 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>64</v>
@@ -2950,7 +2950,7 @@
         <v>65</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>82</v>
@@ -2967,13 +2967,13 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>64</v>
@@ -2982,7 +2982,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>82</v>
@@ -2999,13 +2999,13 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>64</v>
@@ -3014,7 +3014,7 @@
         <v>65</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>82</v>
@@ -3031,13 +3031,13 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>64</v>
@@ -3046,7 +3046,7 @@
         <v>65</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>82</v>
@@ -3063,13 +3063,13 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>64</v>
@@ -3078,7 +3078,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>82</v>
@@ -3095,13 +3095,13 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>64</v>
@@ -3110,7 +3110,7 @@
         <v>65</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>82</v>
@@ -3127,13 +3127,13 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>64</v>
@@ -3142,7 +3142,7 @@
         <v>65</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>82</v>
@@ -3159,13 +3159,13 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>64</v>
@@ -3174,7 +3174,7 @@
         <v>65</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>82</v>
@@ -3191,13 +3191,13 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>64</v>
@@ -3206,7 +3206,7 @@
         <v>65</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>82</v>
@@ -3223,13 +3223,13 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>64</v>
@@ -3238,7 +3238,7 @@
         <v>65</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>82</v>
@@ -3255,13 +3255,13 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>64</v>
@@ -3270,7 +3270,7 @@
         <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>82</v>
@@ -3287,13 +3287,13 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>64</v>
@@ -3302,7 +3302,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>82</v>
@@ -3319,13 +3319,13 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>64</v>
@@ -3334,7 +3334,7 @@
         <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>82</v>
@@ -3351,13 +3351,13 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>64</v>
@@ -3366,7 +3366,7 @@
         <v>65</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>82</v>
@@ -3383,13 +3383,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>64</v>
@@ -3398,7 +3398,7 @@
         <v>65</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>82</v>
@@ -3415,13 +3415,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>64</v>
@@ -3430,7 +3430,7 @@
         <v>65</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>82</v>
@@ -3447,13 +3447,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>64</v>
@@ -3462,7 +3462,7 @@
         <v>65</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>82</v>
@@ -3479,13 +3479,13 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>64</v>
@@ -3494,7 +3494,7 @@
         <v>65</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>82</v>
@@ -3511,13 +3511,13 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>64</v>
@@ -3526,7 +3526,7 @@
         <v>65</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>82</v>
@@ -3543,13 +3543,13 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>64</v>
@@ -3558,7 +3558,7 @@
         <v>65</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>82</v>
@@ -3575,13 +3575,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>64</v>
@@ -3590,7 +3590,7 @@
         <v>65</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>82</v>
@@ -3607,13 +3607,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>64</v>
@@ -3622,7 +3622,7 @@
         <v>65</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>82</v>
@@ -3639,13 +3639,13 @@
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>64</v>
@@ -3654,7 +3654,7 @@
         <v>65</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>82</v>
@@ -6080,7 +6080,7 @@
         <v>87</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>64</v>
@@ -6089,7 +6089,7 @@
         <v>65</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G3" s="6" t="s">
         <v>82</v>
@@ -6112,7 +6112,7 @@
         <v>87</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>64</v>
@@ -6121,7 +6121,7 @@
         <v>65</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>82</v>
@@ -6144,7 +6144,7 @@
         <v>87</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>64</v>
@@ -6153,7 +6153,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>82</v>
@@ -6176,7 +6176,7 @@
         <v>87</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>64</v>
@@ -6185,7 +6185,7 @@
         <v>65</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>82</v>
@@ -6208,7 +6208,7 @@
         <v>87</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>64</v>
@@ -6217,7 +6217,7 @@
         <v>65</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>82</v>
@@ -6240,7 +6240,7 @@
         <v>87</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>64</v>
@@ -6249,7 +6249,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>82</v>
@@ -6272,7 +6272,7 @@
         <v>87</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>64</v>
@@ -6281,7 +6281,7 @@
         <v>65</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>82</v>
@@ -6304,7 +6304,7 @@
         <v>87</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>64</v>
@@ -6313,7 +6313,7 @@
         <v>65</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>82</v>
@@ -6336,7 +6336,7 @@
         <v>87</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>64</v>
@@ -6345,7 +6345,7 @@
         <v>65</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>82</v>
@@ -6368,7 +6368,7 @@
         <v>87</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>64</v>
@@ -6377,7 +6377,7 @@
         <v>65</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>82</v>
@@ -6400,7 +6400,7 @@
         <v>87</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>64</v>
@@ -6409,7 +6409,7 @@
         <v>65</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>82</v>
@@ -6432,7 +6432,7 @@
         <v>87</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>64</v>
@@ -6441,7 +6441,7 @@
         <v>65</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>82</v>
@@ -6464,7 +6464,7 @@
         <v>87</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>64</v>
@@ -6473,7 +6473,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>82</v>
@@ -6496,7 +6496,7 @@
         <v>87</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>64</v>
@@ -6505,7 +6505,7 @@
         <v>65</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>82</v>
@@ -6528,7 +6528,7 @@
         <v>87</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>64</v>
@@ -6537,7 +6537,7 @@
         <v>65</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>82</v>
@@ -6560,7 +6560,7 @@
         <v>87</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>64</v>
@@ -6569,7 +6569,7 @@
         <v>65</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>82</v>
@@ -6592,7 +6592,7 @@
         <v>87</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>64</v>
@@ -6601,7 +6601,7 @@
         <v>65</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>82</v>
@@ -6624,7 +6624,7 @@
         <v>87</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>64</v>
@@ -6633,7 +6633,7 @@
         <v>65</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>82</v>
@@ -6656,7 +6656,7 @@
         <v>87</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>64</v>
@@ -6665,7 +6665,7 @@
         <v>65</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G21" s="6" t="s">
         <v>82</v>
@@ -6688,7 +6688,7 @@
         <v>87</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>64</v>
@@ -6697,7 +6697,7 @@
         <v>65</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G22" s="6" t="s">
         <v>82</v>
@@ -6720,7 +6720,7 @@
         <v>87</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>64</v>
@@ -6729,7 +6729,7 @@
         <v>65</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G23" s="6" t="s">
         <v>82</v>
@@ -6752,7 +6752,7 @@
         <v>87</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>64</v>
@@ -6761,7 +6761,7 @@
         <v>65</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G24" s="6" t="s">
         <v>82</v>
@@ -6784,7 +6784,7 @@
         <v>87</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>64</v>
@@ -6793,7 +6793,7 @@
         <v>65</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G25" s="6" t="s">
         <v>82</v>
@@ -6816,7 +6816,7 @@
         <v>87</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>64</v>
@@ -6825,7 +6825,7 @@
         <v>65</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>82</v>
